--- a/InputData/web-app/CDCF/Cargo Dist Conversion Factors.xlsx
+++ b/InputData/web-app/CDCF/Cargo Dist Conversion Factors.xlsx
@@ -1,39 +1,29 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr defaultThemeVersion="124226"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Meghan\Documents\eps-hongkong\InputData\web-app\CDCF\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160"/>
+    <workbookView xWindow="0" yWindow="60" windowWidth="19140" windowHeight="7090"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
     <sheet name="CDCF-PMpPDOU" sheetId="2" r:id="rId2"/>
     <sheet name="CDCF-FTMpFDOU" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="145621"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>Source:</t>
   </si>
   <si>
+    <t>none needed</t>
+  </si>
+  <si>
     <t>Notes</t>
   </si>
   <si>
@@ -46,44 +36,38 @@
     <t>desired output unit.</t>
   </si>
   <si>
+    <t>For the U.S. model, the desired output units are:</t>
+  </si>
+  <si>
+    <t>trillion passenger-miles</t>
+  </si>
+  <si>
+    <t>trillion freight ton-miles</t>
+  </si>
+  <si>
     <t>CDCF Passenger Miles per Passenger Distance Output Unit</t>
   </si>
   <si>
     <t>passenger distance output unit</t>
   </si>
   <si>
+    <t>passenger-miles</t>
+  </si>
+  <si>
     <t>freight distance output unit</t>
   </si>
   <si>
+    <t>freight ton-miles</t>
+  </si>
+  <si>
     <t>CDCF Freight Ton Miles per Freight Distance Output Unit</t>
   </si>
-  <si>
-    <t>trillion passenger-kilometers</t>
-  </si>
-  <si>
-    <t>trillion freight ton-kilometers</t>
-  </si>
-  <si>
-    <t>Google unit converter</t>
-  </si>
-  <si>
-    <t>https://www.google.com/search?q=kilometers+per+mile</t>
-  </si>
-  <si>
-    <t>passenger-kilometers</t>
-  </si>
-  <si>
-    <t>freight ton-kilometers</t>
-  </si>
-  <si>
-    <t>For the Hong Kong model, the desired output units are:</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -95,14 +79,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -125,21 +101,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -147,9 +120,6 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -198,7 +168,7 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -233,7 +203,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -442,76 +412,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:B14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <dimension ref="A1:B13"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.45">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B5" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="B6" s="4"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A7" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A8" t="s">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A6" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A9" s="2" t="s">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A7" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A10" t="s">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A8" s="2" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A9" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="A11" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
-  <hyperlinks>
-    <hyperlink ref="B5" r:id="rId1"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId2"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -521,24 +480,24 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="20.265625" customWidth="1"/>
-    <col min="2" max="2" width="28.59765625" customWidth="1"/>
+    <col min="1" max="1" width="20.26953125" customWidth="1"/>
+    <col min="2" max="2" width="28.6328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B2">
-        <f>1.60934*10^12</f>
-        <v>1609340000000</v>
+        <f>10^12</f>
+        <v>1000000000000</v>
       </c>
     </row>
   </sheetData>
@@ -552,27 +511,293 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="18.86328125" customWidth="1"/>
-    <col min="2" max="2" width="26.59765625" customWidth="1"/>
+    <col min="1" max="1" width="18.81640625" customWidth="1"/>
+    <col min="2" max="2" width="26.54296875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
       <c r="B1" s="3" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.45">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B2">
-        <f>1.60934*10^12</f>
-        <v>1609340000000</v>
+        <f>10^12</f>
+        <v>1000000000000</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100D257B2780BAD0A45A02FA065B9C6CC6A" ma:contentTypeVersion="17" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="54b727ac31dab95898e9cf92f0402afe">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" xmlns:ns3="6b15a3a4-8173-42d6-9deb-398ec38eca4b" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="42611c3eb46fef4c2b2610d1e51cc1b0" ns2:_="" ns3:_="">
+    <xsd:import namespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433"/>
+    <xsd:import namespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b"/>
+    <xsd:element name="properties">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element name="documentManagement">
+            <xsd:complexType>
+              <xsd:all>
+                <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
+                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceAutoTags" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceLocation" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
+              </xsd:all>
+            </xsd:complexType>
+          </xsd:element>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="cb176f07-3112-4ee9-93fd-ae2cb5f3e433" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceFastMetadata" ma:index="9" nillable="true" ma:displayName="MediaServiceFastMetadata" ma:hidden="true" ma:internalName="MediaServiceFastMetadata" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="12" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceKeyPoints" ma:index="13" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceAutoTags" ma:index="14" nillable="true" ma:displayName="Tags" ma:internalName="MediaServiceAutoTags" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceDateTaken" ma:index="17" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceLocation" ma:index="19" nillable="true" ma:displayName="Location" ma:internalName="MediaServiceLocation" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaLengthInSeconds" ma:index="20" nillable="true" ma:displayName="Length (seconds)" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Unknown"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="22" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Image Tags" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="ca0deac2-43b9-460d-a4eb-012f87ec990e" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
+      <xsd:complexType>
+        <xsd:sequence>
+          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
+        </xsd:sequence>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="24" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="6b15a3a4-8173-42d6-9deb-398ec38eca4b" elementFormDefault="qualified">
+    <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <xsd:element name="SharedWithUsers" ma:index="10" nillable="true" ma:displayName="Shared With" ma:internalName="SharedWithUsers" ma:readOnly="true">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:UserMulti">
+            <xsd:sequence>
+              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
+                <xsd:complexType>
+                  <xsd:sequence>
+                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
+                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
+                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
+                  </xsd:sequence>
+                </xsd:complexType>
+              </xsd:element>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+    <xsd:element name="SharedWithDetails" ma:index="11" nillable="true" ma:displayName="Shared With Details" ma:internalName="SharedWithDetails" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note">
+          <xsd:maxLength value="255"/>
+        </xsd:restriction>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="TaxCatchAll" ma:index="23" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{caf201a3-c970-477d-b8ee-c5923cb026e5}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="6b15a3a4-8173-42d6-9deb-398ec38eca4b">
+      <xsd:complexType>
+        <xsd:complexContent>
+          <xsd:extension base="dms:MultiChoiceLookup">
+            <xsd:sequence>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
+            </xsd:sequence>
+          </xsd:extension>
+        </xsd:complexContent>
+      </xsd:complexType>
+    </xsd:element>
+  </xsd:schema>
+  <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
+    <xsd:import namespace="http://purl.org/dc/elements/1.1/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dc.xsd"/>
+    <xsd:import namespace="http://purl.org/dc/terms/" schemaLocation="http://dublincore.org/schemas/xmls/qdc/2003/04/02/dcterms.xsd"/>
+    <xsd:element name="coreProperties" type="CT_coreProperties"/>
+    <xsd:complexType name="CT_coreProperties">
+      <xsd:all>
+        <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
+        <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
+        <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dc:language" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="category" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="version" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element name="revision" minOccurs="0" maxOccurs="1" type="xsd:string">
+          <xsd:annotation>
+            <xsd:documentation>
+                        This value indicates the number of saves or revisions. The application is responsible for updating this value after each revision.
+                    </xsd:documentation>
+          </xsd:annotation>
+        </xsd:element>
+        <xsd:element name="lastModifiedBy" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+        <xsd:element ref="dcterms:modified" minOccurs="0" maxOccurs="1"/>
+        <xsd:element name="contentStatus" minOccurs="0" maxOccurs="1" type="xsd:string"/>
+      </xsd:all>
+    </xsd:complexType>
+  </xsd:schema>
+  <xs:schema xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" xmlns:xs="http://www.w3.org/2001/XMLSchema" targetNamespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" elementFormDefault="qualified" attributeFormDefault="unqualified">
+    <xs:element name="Person">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:DisplayName" minOccurs="0"/>
+          <xs:element ref="pc:AccountId" minOccurs="0"/>
+          <xs:element ref="pc:AccountType" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="DisplayName" type="xs:string"/>
+    <xs:element name="AccountId" type="xs:string"/>
+    <xs:element name="AccountType" type="xs:string"/>
+    <xs:element name="BDCAssociatedEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:BDCEntity" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+        <xs:attribute ref="pc:EntityNamespace"/>
+        <xs:attribute ref="pc:EntityName"/>
+        <xs:attribute ref="pc:SystemInstanceName"/>
+        <xs:attribute ref="pc:AssociationName"/>
+      </xs:complexType>
+    </xs:element>
+    <xs:attribute name="EntityNamespace" type="xs:string"/>
+    <xs:attribute name="EntityName" type="xs:string"/>
+    <xs:attribute name="SystemInstanceName" type="xs:string"/>
+    <xs:attribute name="AssociationName" type="xs:string"/>
+    <xs:element name="BDCEntity">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:EntityDisplayName" minOccurs="0"/>
+          <xs:element ref="pc:EntityInstanceReference" minOccurs="0"/>
+          <xs:element ref="pc:EntityId1" minOccurs="0"/>
+          <xs:element ref="pc:EntityId2" minOccurs="0"/>
+          <xs:element ref="pc:EntityId3" minOccurs="0"/>
+          <xs:element ref="pc:EntityId4" minOccurs="0"/>
+          <xs:element ref="pc:EntityId5" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="EntityDisplayName" type="xs:string"/>
+    <xs:element name="EntityInstanceReference" type="xs:string"/>
+    <xs:element name="EntityId1" type="xs:string"/>
+    <xs:element name="EntityId2" type="xs:string"/>
+    <xs:element name="EntityId3" type="xs:string"/>
+    <xs:element name="EntityId4" type="xs:string"/>
+    <xs:element name="EntityId5" type="xs:string"/>
+    <xs:element name="Terms">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermInfo" minOccurs="0" maxOccurs="unbounded"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermInfo">
+      <xs:complexType>
+        <xs:sequence>
+          <xs:element ref="pc:TermName" minOccurs="0"/>
+          <xs:element ref="pc:TermId" minOccurs="0"/>
+        </xs:sequence>
+      </xs:complexType>
+    </xs:element>
+    <xs:element name="TermName" type="xs:string"/>
+    <xs:element name="TermId" type="xs:string"/>
+  </xs:schema>
+</ct:contentTypeSchema>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9366628E-F072-48DE-AF8F-189C1F2FCC98}"/>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{AAB997D4-12D2-4C5D-B29A-1DDE4B8EE0A3}"/>
 </file>